--- a/data/trans_orig/P37C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023</t>
+          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>16359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>44258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48324</t>
+          <t>47263</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72396</t>
+          <t>72411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65912</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97202</t>
+          <t>95810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113837</t>
+          <t>115001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147885</t>
+          <t>150861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188145</t>
+          <t>189791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>235001</t>
+          <t>238678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363934</t>
+          <t>363641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399165</t>
+          <t>399197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>564809</t>
+          <t>562805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>600813</t>
+          <t>599494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937017</t>
+          <t>935165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990035</t>
+          <t>989803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>23843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>25620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34266</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57576</t>
+          <t>58458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111168</t>
+          <t>111591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>34298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70521</t>
+          <t>70964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106640</t>
+          <t>109887</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169654</t>
+          <t>170451</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>317643</t>
+          <t>320202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>545233</t>
+          <t>542673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>292125</t>
+          <t>303065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>487251</t>
+          <t>484074</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>705715</t>
+          <t>714704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1002035</t>
+          <t>1007564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1610240</t>
+          <t>1615713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1880842</t>
+          <t>1882976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1667704</t>
+          <t>1669933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1881571</t>
+          <t>1884181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3313403</t>
+          <t>3316054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3655162</t>
+          <t>3639145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>24902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18644</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39889</t>
+          <t>41162</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124707</t>
+          <t>124406</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170064</t>
+          <t>169011</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94937</t>
+          <t>95006</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126171</t>
+          <t>124944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>228389</t>
+          <t>229021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>281800</t>
+          <t>282802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>449388</t>
+          <t>451205</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>496469</t>
+          <t>498288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>516210</t>
+          <t>516925</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>550020</t>
+          <t>551727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>979729</t>
+          <t>981298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1038990</t>
+          <t>1038745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34825</t>
+          <t>35434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17235</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37576</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30534</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56118</t>
+          <t>55012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103595</t>
+          <t>101863</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>162497</t>
+          <t>164081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70182</t>
+          <t>73911</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113147</t>
+          <t>113343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>189131</t>
+          <t>188311</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263898</t>
+          <t>263224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>551986</t>
+          <t>552394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>770613</t>
+          <t>773652</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>534757</t>
+          <t>537960</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>725804</t>
+          <t>727280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1163982</t>
+          <t>1178413</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1461868</t>
+          <t>1465970</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2470993</t>
+          <t>2468825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2740090</t>
+          <t>2744935</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2788554</t>
+          <t>2786286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3021455</t>
+          <t>3008986</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5295504</t>
+          <t>5292633</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5648430</t>
+          <t>5633536</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>428</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16359</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31493</t>
+          <t>39152</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44258</t>
+          <t>52511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20962</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>40563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>59493</t>
+          <t>70762</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47263</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72411</t>
+          <t>90060</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80380</t>
+          <t>94236</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66400</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95810</t>
+          <t>113559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>130557</t>
+          <t>142073</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115001</t>
+          <t>125935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150861</t>
+          <t>160777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>210937</t>
+          <t>236309</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>189791</t>
+          <t>213663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238678</t>
+          <t>261669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>382627</t>
+          <t>419017</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363641</t>
+          <t>398949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399197</t>
+          <t>438326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>582733</t>
+          <t>634951</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>562805</t>
+          <t>617095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>599494</t>
+          <t>653509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>965360</t>
+          <t>1053967</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>935165</t>
+          <t>1026377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>989803</t>
+          <t>1079589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>502702</t>
+          <t>560858</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>502702</t>
+          <t>560858</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>502702</t>
+          <t>560858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>745623</t>
+          <t>813308</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>745623</t>
+          <t>813308</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>745623</t>
+          <t>813308</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1248325</t>
+          <t>1374165</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1248325</t>
+          <t>1374165</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1248325</t>
+          <t>1374165</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14048</t>
+          <t>14726</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>25609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25620</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34784</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86906</t>
+          <t>110237</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58458</t>
+          <t>88051</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111591</t>
+          <t>136529</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>60400</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>46943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70964</t>
+          <t>79353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>139490</t>
+          <t>170637</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109887</t>
+          <t>141965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>170451</t>
+          <t>200039</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>469165</t>
+          <t>518612</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>320202</t>
+          <t>472610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>542673</t>
+          <t>564437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>423387</t>
+          <t>475382</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>303065</t>
+          <t>444279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>484074</t>
+          <t>511303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>892553</t>
+          <t>993995</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>714704</t>
+          <t>934109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1007564</t>
+          <t>1054137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1701185</t>
+          <t>1563595</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1615713</t>
+          <t>1517978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1882976</t>
+          <t>1612806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1741311</t>
+          <t>1613152</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1669933</t>
+          <t>1576097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1884181</t>
+          <t>1645674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3442496</t>
+          <t>3176747</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3316054</t>
+          <t>3111094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3639145</t>
+          <t>3240137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2278213</t>
+          <t>2215985</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2278213</t>
+          <t>2215985</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2278213</t>
+          <t>2215985</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2234127</t>
+          <t>2167223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2234127</t>
+          <t>2167223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2234127</t>
+          <t>2167223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4512340</t>
+          <t>4383208</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4512340</t>
+          <t>4383208</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4512340</t>
+          <t>4383208</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>611</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24902</t>
+          <t>28353</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>26926</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41162</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>145076</t>
+          <t>165019</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124406</t>
+          <t>143222</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169011</t>
+          <t>190358</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>110039</t>
+          <t>124009</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95006</t>
+          <t>106834</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124944</t>
+          <t>141702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>255115</t>
+          <t>289028</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>229021</t>
+          <t>258309</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>282802</t>
+          <t>320925</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>476044</t>
+          <t>518851</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>451205</t>
+          <t>492511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>498288</t>
+          <t>541841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>533740</t>
+          <t>590528</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>516925</t>
+          <t>570259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>551727</t>
+          <t>608513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1009784</t>
+          <t>1109380</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>981298</t>
+          <t>1077958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1038745</t>
+          <t>1143244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645898</t>
+          <t>710919</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645898</t>
+          <t>710919</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645898</t>
+          <t>710919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1306361</t>
+          <t>1445797</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1306361</t>
+          <t>1445797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1306361</t>
+          <t>1445797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35434</t>
+          <t>33740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17218</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>44053</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>47884</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>55012</t>
+          <t>62996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>133877</t>
+          <t>166341</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>101863</t>
+          <t>140771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>164081</t>
+          <t>198943</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>92033</t>
+          <t>106602</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73911</t>
+          <t>87563</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113343</t>
+          <t>127990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>225909</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>188311</t>
+          <t>239936</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263224</t>
+          <t>312226</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>694621</t>
+          <t>777868</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>552394</t>
+          <t>726519</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>773652</t>
+          <t>834529</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>663984</t>
+          <t>741464</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>537960</t>
+          <t>702180</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>727280</t>
+          <t>785846</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1358605</t>
+          <t>1519332</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1178413</t>
+          <t>1452572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1465970</t>
+          <t>1588134</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2559857</t>
+          <t>2501464</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2468825</t>
+          <t>2442031</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2744935</t>
+          <t>2561258</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2857783</t>
+          <t>2838631</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2786286</t>
+          <t>2791332</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3008986</t>
+          <t>2884159</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5417640</t>
+          <t>5340094</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5292633</t>
+          <t>5268948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5633536</t>
+          <t>5420095</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3426814</t>
+          <t>3487763</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3426814</t>
+          <t>3487763</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3426814</t>
+          <t>3487763</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3640213</t>
+          <t>3715408</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3640213</t>
+          <t>3715408</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3640213</t>
+          <t>3715408</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7067027</t>
+          <t>7203170</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7067027</t>
+          <t>7203170</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7067027</t>
+          <t>7203170</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
